--- a/Scripts/python/varadero_annual.xlsx
+++ b/Scripts/python/varadero_annual.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GDrive\Academicos\Articulos\Pendientes\Varadero growth rates\data\python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GDrive\Academicos\Articulos\Pendientes\Varadero growth rates\Scripts\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AB4541-F697-48C0-B936-214F21E40307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96A433A1-87C8-4337-92D9-20D1BF0F1B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{3159E436-0856-4AF4-B48D-2DBAA427E8C8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3159E436-0856-4AF4-B48D-2DBAA427E8C8}"/>
   </bookViews>
   <sheets>
     <sheet name="growth" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Hoja2_HID" sheetId="7" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">environmental!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">environmental!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">growth!$A$1:$G$2857</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'growth-annual'!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">luminescence!$A$1:$E$1</definedName>
@@ -76,7 +76,7 @@
     <author>Luis Lizcano</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{D5719B14-CAE2-473E-9E62-AD151D515365}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{75D25D34-2738-450A-B01C-717777D6B7D1}">
       <text>
         <r>
           <rPr>
@@ -100,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{BBE1963D-0CCE-4AB2-A778-9755B42323FC}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{BBE1963D-0CCE-4AB2-A778-9755B42323FC}">
       <text>
         <r>
           <rPr>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="42">
   <si>
     <t>Core</t>
   </si>
@@ -159,12 +159,6 @@
   </si>
   <si>
     <t>G/B</t>
-  </si>
-  <si>
-    <t>WaterFlow</t>
-  </si>
-  <si>
-    <t>Temperature</t>
   </si>
   <si>
     <t>SOI</t>
@@ -252,6 +246,15 @@
   </si>
   <si>
     <t>Prueba t para dos muestras suponiendo varianzas desiguales</t>
+  </si>
+  <si>
+    <t>WF_Helena</t>
+  </si>
+  <si>
+    <t>WF_Calamar</t>
+  </si>
+  <si>
+    <t>Air_Temperature</t>
   </si>
 </sst>
 </file>
@@ -1155,6 +1158,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1162,7 +1166,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1869,6 +1872,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1876,7 +1880,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2628,6 +2631,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2635,7 +2639,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3437,6 +3440,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3444,7 +3448,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4246,6 +4249,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4253,7 +4257,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4825,6 +4828,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4832,7 +4836,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5454,6 +5457,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5461,7 +5465,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6083,6 +6086,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6090,7 +6094,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -25808,7 +25811,7 @@
         <v>9</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -28982,101 +28985,110 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C301A6-E881-46D2-940A-627C9E4E5D1E}">
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2015</v>
       </c>
       <c r="B2" s="4">
         <v>259.74166666666667</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
+        <v>4608.416666666667</v>
+      </c>
+      <c r="D2" s="5">
         <v>28.392886867412198</v>
       </c>
-      <c r="D2" s="4">
+      <c r="E2" s="4">
         <v>-0.79166666666666663</v>
       </c>
-      <c r="E2" s="4">
+      <c r="F2" s="4">
         <v>0.10616666666666667</v>
       </c>
-      <c r="F2" s="4">
+      <c r="G2" s="4">
         <v>42.81413229580177</v>
       </c>
-      <c r="G2" s="5">
+      <c r="H2" s="5">
         <v>0.679450370629058</v>
       </c>
-      <c r="H2" s="4">
+      <c r="I2" s="4">
         <v>0.58225007644065752</v>
       </c>
-      <c r="I2" s="4">
+      <c r="J2" s="4">
         <v>0.14583541989849277</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L2" s="6"/>
+      <c r="M2" s="7"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2014</v>
       </c>
       <c r="B3" s="4">
         <v>326.30833333333334</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
+        <v>5799.083333333333</v>
+      </c>
+      <c r="D3" s="5">
         <v>28.249761100998459</v>
       </c>
-      <c r="D3" s="4">
+      <c r="E3" s="4">
         <v>-0.13333333333333333</v>
       </c>
-      <c r="E3" s="4">
+      <c r="F3" s="4">
         <v>9.3750000000000014E-2</v>
       </c>
-      <c r="F3" s="4">
+      <c r="G3" s="4">
         <v>110.31511442090333</v>
       </c>
-      <c r="G3" s="5">
+      <c r="H3" s="5">
         <v>0.61480570312082772</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3" s="4">
         <v>0.74141551757227853</v>
       </c>
-      <c r="I3" s="4">
+      <c r="J3" s="4">
         <v>0.15980392815743127</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L3" s="6"/>
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2013</v>
       </c>
@@ -29084,29 +29096,32 @@
         <v>294.05</v>
       </c>
       <c r="C4" s="4">
+        <v>6146.416666666667</v>
+      </c>
+      <c r="D4" s="4">
         <v>28.191666666666666</v>
       </c>
-      <c r="D4" s="4">
+      <c r="E4" s="4">
         <v>0.45</v>
       </c>
-      <c r="E4" s="4">
+      <c r="F4" s="4">
         <v>0.1585</v>
       </c>
-      <c r="F4" s="4">
+      <c r="G4" s="4">
         <v>98.445162400191023</v>
       </c>
-      <c r="G4" s="4">
+      <c r="H4" s="4">
         <v>0.57280542997257011</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <v>0.54522722535904911</v>
       </c>
-      <c r="I4" s="4">
+      <c r="J4" s="4">
         <v>8.6077660495413363E-2</v>
       </c>
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4" s="7"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2012</v>
       </c>
@@ -29114,29 +29129,32 @@
         <v>356.47499999999997</v>
       </c>
       <c r="C5" s="4">
+        <v>7361.5</v>
+      </c>
+      <c r="D5" s="4">
         <v>28.141176055555551</v>
       </c>
-      <c r="D5" s="4">
+      <c r="E5" s="4">
         <v>0.13333333333333333</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F5" s="4">
         <v>0.20516666666666664</v>
       </c>
-      <c r="F5" s="4">
+      <c r="G5" s="4">
         <v>93.313032559522711</v>
       </c>
-      <c r="G5" s="4">
+      <c r="H5" s="4">
         <v>0.78846362383865531</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="4">
         <v>0.48679533375916517</v>
       </c>
-      <c r="I5" s="4">
+      <c r="J5" s="4">
         <v>0.17366207171260847</v>
       </c>
-      <c r="L5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" s="7"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2011</v>
       </c>
@@ -29144,29 +29162,32 @@
         <v>515.89166666666677</v>
       </c>
       <c r="C6" s="4">
+        <v>10223.916666666666</v>
+      </c>
+      <c r="D6" s="4">
         <v>27.712500000000002</v>
       </c>
-      <c r="D6" s="4">
+      <c r="E6" s="4">
         <v>1.4000000000000001</v>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="4">
         <v>9.3666666666666662E-2</v>
       </c>
-      <c r="F6" s="4">
+      <c r="G6" s="4">
         <v>110.24948945116429</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H6" s="4">
         <v>0.5502582038544187</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
         <v>0.92343233251130674</v>
       </c>
-      <c r="I6" s="4">
+      <c r="J6" s="4">
         <v>7.7873245882282477E-2</v>
       </c>
-      <c r="L6" s="7"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6" s="7"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2010</v>
       </c>
@@ -29174,29 +29195,32 @@
         <v>465.34166666666653</v>
       </c>
       <c r="C7" s="4">
+        <v>9012.1666666666661</v>
+      </c>
+      <c r="D7" s="4">
         <v>28.133333333333329</v>
       </c>
-      <c r="D7" s="4">
+      <c r="E7" s="4">
         <v>0.90833333333333366</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>0.34116666666666667</v>
       </c>
-      <c r="F7" s="4">
+      <c r="G7" s="4">
         <v>244.57666750505638</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="4">
         <v>0.58826916123540429</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
         <v>1.3740837167385618</v>
       </c>
-      <c r="I7" s="4">
+      <c r="J7" s="4">
         <v>0.14756313492156098</v>
       </c>
-      <c r="L7" s="7"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7" s="7"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2009</v>
       </c>
@@ -29204,28 +29228,31 @@
         <v>419.25833333333338</v>
       </c>
       <c r="C8" s="4">
+        <v>6946.25</v>
+      </c>
+      <c r="D8" s="4">
         <v>28.166666666666661</v>
       </c>
-      <c r="D8" s="4">
+      <c r="E8" s="4">
         <v>0.16666666666666666</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <v>3.0416666666666651E-2</v>
       </c>
-      <c r="F8" s="4">
+      <c r="G8" s="4">
         <v>76.471628230621533</v>
       </c>
-      <c r="G8" s="4">
+      <c r="H8" s="4">
         <v>0.74264066109737903</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="4">
         <v>0.84027412554511405</v>
       </c>
-      <c r="I8" s="4">
+      <c r="J8" s="4">
         <v>0.13534498569032824</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2008</v>
       </c>
@@ -29233,28 +29260,31 @@
         <v>560.5</v>
       </c>
       <c r="C9" s="4">
+        <v>9878.4166666666661</v>
+      </c>
+      <c r="D9" s="4">
         <v>27.633333333333329</v>
       </c>
-      <c r="D9" s="4">
+      <c r="E9" s="4">
         <v>1.125</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <v>0.12925</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G9" s="4">
         <v>114.71403972091167</v>
       </c>
-      <c r="G9" s="4">
+      <c r="H9" s="4">
         <v>0.49604496374885815</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4">
         <v>0.70726746901527471</v>
       </c>
-      <c r="I9" s="4">
+      <c r="J9" s="4">
         <v>8.4159075565265085E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2007</v>
       </c>
@@ -29262,28 +29292,31 @@
         <v>512.25833333333333</v>
       </c>
       <c r="C10" s="4">
+        <v>8904.25</v>
+      </c>
+      <c r="D10" s="4">
         <v>27.775000000000002</v>
       </c>
-      <c r="D10" s="4">
+      <c r="E10" s="4">
         <v>0.26666666666666661</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <v>0.13841666666666666</v>
       </c>
-      <c r="F10" s="4">
+      <c r="G10" s="4">
         <v>140.53287844573006</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="4">
         <v>0.51895874770368944</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4">
         <v>0.6457319079693189</v>
       </c>
-      <c r="I10" s="4">
+      <c r="J10" s="4">
         <v>4.4679583161833056E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2006</v>
       </c>
@@ -29291,28 +29324,31 @@
         <v>482.4083333333333</v>
       </c>
       <c r="C11" s="4">
+        <v>8022.416666666667</v>
+      </c>
+      <c r="D11" s="4">
         <v>27.974999999999998</v>
       </c>
-      <c r="D11" s="4">
+      <c r="E11" s="4">
         <v>2.4999999999999984E-2</v>
       </c>
-      <c r="E11" s="4">
+      <c r="F11" s="4">
         <v>0.25741666666666668</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="4">
         <v>94.013514099481128</v>
       </c>
-      <c r="G11" s="4">
+      <c r="H11" s="4">
         <v>0.65522376469278132</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <v>1.0064564299832086</v>
       </c>
-      <c r="I11" s="4">
+      <c r="J11" s="4">
         <v>0.12129487610652377</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2005</v>
       </c>
@@ -29320,28 +29356,31 @@
         <v>401.79999999999995</v>
       </c>
       <c r="C12" s="4">
+        <v>7210.166666666667</v>
+      </c>
+      <c r="D12" s="4">
         <v>28.133333333333336</v>
       </c>
-      <c r="D12" s="4">
+      <c r="E12" s="4">
         <v>-0.18333333333333338</v>
       </c>
-      <c r="E12" s="4">
+      <c r="F12" s="4">
         <v>0.28266666666666668</v>
       </c>
-      <c r="F12" s="4">
+      <c r="G12" s="4">
         <v>103.43755252676506</v>
       </c>
-      <c r="G12" s="4">
+      <c r="H12" s="4">
         <v>0.52627910557963176</v>
       </c>
-      <c r="H12" s="4">
+      <c r="I12" s="4">
         <v>1.0581573463795304</v>
       </c>
-      <c r="I12" s="4">
+      <c r="J12" s="4">
         <v>0.1180634138798707</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2004</v>
       </c>
@@ -29349,28 +29388,31 @@
         <v>370.78333333333336</v>
       </c>
       <c r="C13" s="4">
+        <v>6657.833333333333</v>
+      </c>
+      <c r="D13" s="4">
         <v>27.858333333333331</v>
       </c>
-      <c r="D13" s="4">
+      <c r="E13" s="4">
         <v>-0.25833333333333336</v>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="4">
         <v>0.19674999999999998</v>
       </c>
-      <c r="F13" s="4">
+      <c r="G13" s="4">
         <v>136.4003987819639</v>
       </c>
-      <c r="G13" s="4">
+      <c r="H13" s="4">
         <v>0.52821884812561493</v>
       </c>
-      <c r="H13" s="4">
+      <c r="I13" s="4">
         <v>0.76924796018086683</v>
       </c>
-      <c r="I13" s="4">
+      <c r="J13" s="4">
         <v>7.7410505512083852E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2003</v>
       </c>
@@ -29378,28 +29420,31 @@
         <v>366.98333333333335</v>
       </c>
       <c r="C14" s="4">
+        <v>6293.666666666667</v>
+      </c>
+      <c r="D14" s="4">
         <v>28.025000000000002</v>
       </c>
-      <c r="D14" s="4">
+      <c r="E14" s="4">
         <v>-9.166666666666666E-2</v>
       </c>
-      <c r="E14" s="4">
+      <c r="F14" s="4">
         <v>0.22158333333333335</v>
       </c>
-      <c r="F14" s="4">
+      <c r="G14" s="4">
         <v>132.21796627561852</v>
       </c>
-      <c r="G14" s="4">
+      <c r="H14" s="4">
         <v>0.46539328432080884</v>
       </c>
-      <c r="H14" s="4">
+      <c r="I14" s="4">
         <v>0.46604395682914906</v>
       </c>
-      <c r="I14" s="4">
+      <c r="J14" s="4">
         <v>0.15272164717272893</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2002</v>
       </c>
@@ -29407,57 +29452,63 @@
         <v>361.55833333333334</v>
       </c>
       <c r="C15" s="4">
+        <v>5473.25</v>
+      </c>
+      <c r="D15" s="4">
         <v>28.049999999999997</v>
       </c>
-      <c r="D15" s="4">
+      <c r="E15" s="4">
         <v>-0.3249999999999999</v>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" s="4">
         <v>5.5333333333333345E-2</v>
       </c>
-      <c r="F15" s="4">
+      <c r="G15" s="4">
         <v>83.460774219589879</v>
       </c>
-      <c r="G15" s="4">
+      <c r="H15" s="4">
         <v>0.66674241993850569</v>
       </c>
-      <c r="H15" s="4">
+      <c r="I15" s="4">
         <v>0.60771554350549717</v>
       </c>
-      <c r="I15" s="4">
+      <c r="J15" s="4">
         <v>9.6139418964272291E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2001</v>
       </c>
       <c r="B16" s="4">
         <v>284.84999999999997</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="4">
+        <v>5162.333333333333</v>
+      </c>
+      <c r="D16" s="9">
         <v>27.708333333333332</v>
       </c>
-      <c r="D16" s="4">
+      <c r="E16" s="4">
         <v>0.2583333333333333</v>
       </c>
-      <c r="E16" s="4">
+      <c r="F16" s="4">
         <v>0.10933333333333332</v>
       </c>
-      <c r="F16" s="4">
+      <c r="G16" s="4">
         <v>82.369814638836928</v>
       </c>
-      <c r="G16" s="4">
+      <c r="H16" s="4">
         <v>0.80955468492177129</v>
       </c>
-      <c r="H16" s="4">
+      <c r="I16" s="4">
         <v>0.71663142971865679</v>
       </c>
-      <c r="I16" s="4">
+      <c r="J16" s="4">
         <v>0.13149927986898105</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2000</v>
       </c>
@@ -29465,28 +29516,31 @@
         <v>511.77500000000003</v>
       </c>
       <c r="C17" s="4">
+        <v>8423.1666666666661</v>
+      </c>
+      <c r="D17" s="4">
         <v>27.383333333333336</v>
       </c>
-      <c r="D17" s="4">
+      <c r="E17" s="4">
         <v>0.85</v>
       </c>
-      <c r="E17" s="4">
+      <c r="F17" s="4">
         <v>1.8583333333333327E-2</v>
       </c>
-      <c r="F17" s="4">
+      <c r="G17" s="4">
         <v>79.960866849182224</v>
       </c>
-      <c r="G17" s="4">
+      <c r="H17" s="4">
         <v>0.72592678485484796</v>
       </c>
-      <c r="H17" s="4">
+      <c r="I17" s="4">
         <v>0.6374665766639348</v>
       </c>
-      <c r="I17" s="4">
+      <c r="J17" s="4">
         <v>8.3231832124421479E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1999</v>
       </c>
@@ -29494,28 +29548,31 @@
         <v>537.83333333333337</v>
       </c>
       <c r="C18" s="4">
+        <v>10123.5</v>
+      </c>
+      <c r="D18" s="4">
         <v>27.408333333333335</v>
       </c>
-      <c r="D18" s="4">
+      <c r="E18" s="4">
         <v>0.85</v>
       </c>
-      <c r="E18" s="4">
+      <c r="F18" s="4">
         <v>0.108</v>
       </c>
-      <c r="F18" s="4">
+      <c r="G18" s="4">
         <v>54.470431233724213</v>
       </c>
-      <c r="G18" s="4">
+      <c r="H18" s="4">
         <v>0.57754705960692587</v>
       </c>
-      <c r="H18" s="4">
+      <c r="I18" s="4">
         <v>0.58231512868111979</v>
       </c>
-      <c r="I18" s="4">
+      <c r="J18" s="4">
         <v>0.10141633363158385</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1998</v>
       </c>
@@ -29523,28 +29580,31 @@
         <v>358.34166666666664</v>
       </c>
       <c r="C19" s="4">
+        <v>6857</v>
+      </c>
+      <c r="D19" s="4">
         <v>28.099999999999998</v>
       </c>
-      <c r="D19" s="4">
+      <c r="E19" s="4">
         <v>-2.4999999999999984E-2</v>
       </c>
-      <c r="E19" s="4">
+      <c r="F19" s="4">
         <v>0.36258333333333331</v>
       </c>
-      <c r="F19" s="4">
+      <c r="G19" s="4">
         <v>160.38663772461251</v>
       </c>
-      <c r="G19" s="4">
+      <c r="H19" s="4">
         <v>0.51698426211319737</v>
       </c>
-      <c r="H19" s="4">
+      <c r="I19" s="4">
         <v>1.5995027636453432</v>
       </c>
-      <c r="I19" s="4">
+      <c r="J19" s="4">
         <v>0.10970162701481209</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1997</v>
       </c>
@@ -29552,28 +29612,31 @@
         <v>214.61666666666665</v>
       </c>
       <c r="C20" s="4">
+        <v>4667.833333333333</v>
+      </c>
+      <c r="D20" s="4">
         <v>27.766666666666666</v>
       </c>
-      <c r="D20" s="4">
+      <c r="E20" s="4">
         <v>-0.73333333333333339</v>
       </c>
-      <c r="E20" s="4">
+      <c r="F20" s="4">
         <v>4.200000000000001E-2</v>
       </c>
-      <c r="F20" s="4">
+      <c r="G20" s="4">
         <v>52.573028572960673</v>
       </c>
-      <c r="G20" s="4">
+      <c r="H20" s="4">
         <v>0.79238802860643243</v>
       </c>
-      <c r="H20" s="4">
+      <c r="I20" s="4">
         <v>0.95853423454140574</v>
       </c>
-      <c r="I20" s="4">
+      <c r="J20" s="4">
         <v>6.9295152657441933E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1996</v>
       </c>
@@ -29581,28 +29644,31 @@
         <v>407.42499999999995</v>
       </c>
       <c r="C21" s="4">
+        <v>8578.5</v>
+      </c>
+      <c r="D21" s="4">
         <v>27.691666666666666</v>
       </c>
-      <c r="D21" s="9">
+      <c r="E21" s="9">
         <v>0.67500000000000016</v>
       </c>
-      <c r="E21" s="9">
+      <c r="F21" s="9">
         <v>-6.7750000000000019E-2</v>
       </c>
-      <c r="F21" s="4">
+      <c r="G21" s="4">
         <v>62.756066349289341</v>
       </c>
-      <c r="G21" s="4">
+      <c r="H21" s="4">
         <v>0.4294993561924127</v>
       </c>
-      <c r="H21" s="4">
+      <c r="I21" s="4">
         <v>0.37203372281164337</v>
       </c>
-      <c r="I21" s="4">
+      <c r="J21" s="4">
         <v>6.5783563849393809E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1995</v>
       </c>
@@ -29610,28 +29676,31 @@
         <v>391.52500000000003</v>
       </c>
       <c r="C22" s="4">
+        <v>6814.5</v>
+      </c>
+      <c r="D22" s="4">
         <v>27.791666666666668</v>
       </c>
-      <c r="D22" s="4">
+      <c r="E22" s="4">
         <v>-1.6666666666666666E-2</v>
       </c>
-      <c r="E22" s="4">
+      <c r="F22" s="4">
         <v>0.12491666666666666</v>
       </c>
-      <c r="F22" s="4">
+      <c r="G22" s="4">
         <v>171.37675203003354</v>
       </c>
-      <c r="G22" s="4">
+      <c r="H22" s="4">
         <v>0.59765957676336945</v>
       </c>
-      <c r="H22" s="4">
+      <c r="I22" s="4">
         <v>0.43239992711573966</v>
       </c>
-      <c r="I22" s="4">
+      <c r="J22" s="4">
         <v>0.1368891112831068</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1994</v>
       </c>
@@ -29639,28 +29708,31 @@
         <v>384.99999999999994</v>
       </c>
       <c r="C23" s="4">
+        <v>7598.083333333333</v>
+      </c>
+      <c r="D23" s="4">
         <v>27.5</v>
       </c>
-      <c r="D23" s="4">
+      <c r="E23" s="4">
         <v>-0.82499999999999984</v>
       </c>
-      <c r="E23" s="4">
+      <c r="F23" s="4">
         <v>-0.1869166666666667</v>
       </c>
-      <c r="F23" s="4">
+      <c r="G23" s="4">
         <v>81.875881674642528</v>
       </c>
-      <c r="G23" s="4">
+      <c r="H23" s="4">
         <v>0.6646940512883972</v>
       </c>
-      <c r="H23" s="4">
+      <c r="I23" s="4">
         <v>0.56104610084442019</v>
       </c>
-      <c r="I23" s="4">
+      <c r="J23" s="4">
         <v>9.3190380242259785E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1993</v>
       </c>
@@ -29668,28 +29740,31 @@
         <v>324.16666666666669</v>
       </c>
       <c r="C24" s="4">
+        <v>6861.916666666667</v>
+      </c>
+      <c r="D24" s="4">
         <v>27.791666666666668</v>
       </c>
-      <c r="D24" s="4">
+      <c r="E24" s="4">
         <v>-0.65</v>
       </c>
-      <c r="E24" s="4">
+      <c r="F24" s="4">
         <v>-0.22058333333333333</v>
       </c>
-      <c r="F24" s="4">
+      <c r="G24" s="4">
         <v>103.54616303266781</v>
       </c>
-      <c r="G24" s="4">
+      <c r="H24" s="4">
         <v>0.54848275573014449</v>
       </c>
-      <c r="H24" s="4">
+      <c r="I24" s="4">
         <v>0.41009976613236226</v>
       </c>
-      <c r="I24" s="4">
+      <c r="J24" s="4">
         <v>5.2612577710404451E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1992</v>
       </c>
@@ -29697,28 +29772,31 @@
         <v>248.8416666666667</v>
       </c>
       <c r="C25" s="4">
+        <v>5090.166666666667</v>
+      </c>
+      <c r="D25" s="4">
         <v>27.775000000000002</v>
       </c>
-      <c r="D25" s="4">
+      <c r="E25" s="4">
         <v>-0.82500000000000007</v>
       </c>
-      <c r="E25" s="4">
+      <c r="F25" s="4">
         <v>-0.22925000000000004</v>
       </c>
-      <c r="F25" s="4">
+      <c r="G25" s="4">
         <v>88.447225747471705</v>
       </c>
-      <c r="G25" s="4">
+      <c r="H25" s="4">
         <v>0.57544449222871441</v>
       </c>
-      <c r="H25" s="4">
+      <c r="I25" s="4">
         <v>0.9459242714259567</v>
       </c>
-      <c r="I25" s="4">
+      <c r="J25" s="4">
         <v>9.9408363467430177E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1991</v>
       </c>
@@ -29726,28 +29804,31 @@
         <v>242.79999999999998</v>
       </c>
       <c r="C26" s="4">
+        <v>6351.75</v>
+      </c>
+      <c r="D26" s="4">
         <v>27.625</v>
       </c>
-      <c r="D26" s="9">
+      <c r="E26" s="9">
         <v>-0.57500000000000007</v>
       </c>
-      <c r="E26" s="4">
+      <c r="F26" s="4">
         <v>-0.14241666666666669</v>
       </c>
-      <c r="F26" s="4">
+      <c r="G26" s="4">
         <v>56.543627564755951</v>
       </c>
-      <c r="G26" s="4">
+      <c r="H26" s="4">
         <v>0.67973925482162234</v>
       </c>
-      <c r="H26" s="4">
+      <c r="I26" s="4">
         <v>0.70598094231295705</v>
       </c>
-      <c r="I26" s="4">
+      <c r="J26" s="4">
         <v>7.1288732162476581E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1990</v>
       </c>
@@ -29755,28 +29836,31 @@
         <v>316.10833333333335</v>
       </c>
       <c r="C27" s="4">
+        <v>7076</v>
+      </c>
+      <c r="D27" s="4">
         <v>27.474999999999998</v>
       </c>
-      <c r="D27" s="4">
+      <c r="E27" s="4">
         <v>-0.11666666666666665</v>
       </c>
-      <c r="E27" s="4">
+      <c r="F27" s="4">
         <v>-4.8583333333333333E-2</v>
       </c>
-      <c r="F27" s="4">
+      <c r="G27" s="4">
         <v>90.994240160706042</v>
       </c>
-      <c r="G27" s="4">
+      <c r="H27" s="4">
         <v>0.55288499543921221</v>
       </c>
-      <c r="H27" s="4">
+      <c r="I27" s="4">
         <v>0.73711147958319945</v>
       </c>
-      <c r="I27" s="4">
+      <c r="J27" s="4">
         <v>0.12500796944292161</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1989</v>
       </c>
@@ -29784,28 +29868,31 @@
         <v>369.30833333333334</v>
       </c>
       <c r="C28" s="4">
+        <v>8372.5833333333339</v>
+      </c>
+      <c r="D28" s="4">
         <v>27.574999999999999</v>
       </c>
-      <c r="D28" s="4">
+      <c r="E28" s="4">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E28" s="4">
+      <c r="F28" s="4">
         <v>-9.3083333333333337E-2</v>
       </c>
-      <c r="F28" s="4">
+      <c r="G28" s="4">
         <v>117.01617182978177</v>
       </c>
-      <c r="G28" s="4">
+      <c r="H28" s="4">
         <v>0.52418768325164555</v>
       </c>
-      <c r="H28" s="4">
+      <c r="I28" s="4">
         <v>0.70383150531841632</v>
       </c>
-      <c r="I28" s="4">
+      <c r="J28" s="4">
         <v>0.14884125670313891</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1988</v>
       </c>
@@ -29813,28 +29900,31 @@
         <v>437.18333333333334</v>
       </c>
       <c r="C29" s="4">
+        <v>8442.25</v>
+      </c>
+      <c r="D29" s="4">
         <v>27.508333333333336</v>
       </c>
-      <c r="D29" s="4">
+      <c r="E29" s="4">
         <v>0.81666666666666654</v>
       </c>
-      <c r="E29" s="4">
+      <c r="F29" s="4">
         <v>-1.5166666666666674E-2</v>
       </c>
-      <c r="F29" s="4">
+      <c r="G29" s="4">
         <v>209.02754421947421</v>
       </c>
-      <c r="G29" s="4">
+      <c r="H29" s="4">
         <v>0.5401318581998511</v>
       </c>
-      <c r="H29" s="4">
+      <c r="I29" s="4">
         <v>0.74691283820723564</v>
       </c>
-      <c r="I29" s="4">
+      <c r="J29" s="4">
         <v>0.1193778061704126</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1987</v>
       </c>
@@ -29842,28 +29932,31 @@
         <v>312.54166666666669</v>
       </c>
       <c r="C30" s="4">
+        <v>6941.25</v>
+      </c>
+      <c r="D30" s="4">
         <v>27.966666666666669</v>
       </c>
-      <c r="D30" s="4">
+      <c r="E30" s="4">
         <v>-0.93333333333333313</v>
       </c>
-      <c r="E30" s="4">
+      <c r="F30" s="4">
         <v>5.6166666666666663E-2</v>
       </c>
-      <c r="F30" s="4">
+      <c r="G30" s="4">
         <v>168.10687865615472</v>
       </c>
-      <c r="G30" s="4">
+      <c r="H30" s="4">
         <v>0.67059448976036873</v>
       </c>
-      <c r="H30" s="4">
+      <c r="I30" s="4">
         <v>0.44789067930250676</v>
       </c>
-      <c r="I30" s="4">
+      <c r="J30" s="4">
         <v>0.17844624010065496</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1986</v>
       </c>
@@ -29871,28 +29964,31 @@
         <v>317.27500000000003</v>
       </c>
       <c r="C31" s="4">
+        <v>7595.166666666667</v>
+      </c>
+      <c r="D31" s="4">
         <v>27.666666666666668</v>
       </c>
-      <c r="D31" s="4">
+      <c r="E31" s="4">
         <v>-8.3333333333333301E-2</v>
       </c>
-      <c r="E31" s="4">
+      <c r="F31" s="4">
         <v>-0.28533333333333338</v>
       </c>
-      <c r="F31" s="4">
+      <c r="G31" s="4">
         <v>97.652464708456492</v>
       </c>
-      <c r="G31" s="4">
+      <c r="H31" s="4">
         <v>0.71393064768012948</v>
       </c>
-      <c r="H31" s="4">
+      <c r="I31" s="4">
         <v>0.82883635113917209</v>
       </c>
-      <c r="I31" s="4">
+      <c r="J31" s="4">
         <v>5.5828199673533051E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1985</v>
       </c>
@@ -29900,28 +29996,31 @@
         <v>304.03333333333336</v>
       </c>
       <c r="C32" s="4">
+        <v>6495.833333333333</v>
+      </c>
+      <c r="D32" s="4">
         <v>27.466666666666665</v>
       </c>
-      <c r="D32" s="4">
+      <c r="E32" s="4">
         <v>0.28333333333333338</v>
       </c>
-      <c r="E32" s="4">
+      <c r="F32" s="4">
         <v>-0.27758333333333335</v>
       </c>
-      <c r="F32" s="4">
+      <c r="G32" s="4">
         <v>117.23220418029209</v>
       </c>
-      <c r="G32" s="4">
+      <c r="H32" s="4">
         <v>0.83702213865946284</v>
       </c>
-      <c r="H32" s="4">
+      <c r="I32" s="4">
         <v>0.61913918736689022</v>
       </c>
-      <c r="I32" s="4">
+      <c r="J32" s="4">
         <v>8.2946267748062852E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1984</v>
       </c>
@@ -29929,28 +30028,31 @@
         <v>362.58333333333331</v>
       </c>
       <c r="C33" s="4">
+        <v>8824.1666666666661</v>
+      </c>
+      <c r="D33" s="4">
         <v>27.391666666666666</v>
       </c>
-      <c r="D33" s="4">
+      <c r="E33" s="4">
         <v>0.14166666666666666</v>
       </c>
-      <c r="E33" s="4">
+      <c r="F33" s="4">
         <v>-0.2183333333333333</v>
       </c>
-      <c r="F33" s="4">
+      <c r="G33" s="4">
         <v>156.9116186284688</v>
       </c>
-      <c r="G33" s="4">
+      <c r="H33" s="4">
         <v>0.53505876199523994</v>
       </c>
-      <c r="H33" s="4">
+      <c r="I33" s="4">
         <v>0.3396745322787505</v>
       </c>
-      <c r="I33" s="4">
+      <c r="J33" s="4">
         <v>0.10658273212804595</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1983</v>
       </c>
@@ -29958,28 +30060,31 @@
         <v>157.01666666666668</v>
       </c>
       <c r="C34" s="4">
+        <v>5919.416666666667</v>
+      </c>
+      <c r="D34" s="4">
         <v>28.116666666666664</v>
       </c>
-      <c r="D34" s="4">
+      <c r="E34" s="4">
         <v>-0.7583333333333333</v>
       </c>
-      <c r="E34" s="4">
+      <c r="F34" s="4">
         <v>-8.1416666666666679E-2</v>
       </c>
-      <c r="F34" s="4">
+      <c r="G34" s="4">
         <v>103.86205793641811</v>
       </c>
-      <c r="G34" s="4">
+      <c r="H34" s="4">
         <v>0.62498484830118961</v>
       </c>
-      <c r="H34" s="4">
+      <c r="I34" s="4">
         <v>1.5547337295167201</v>
       </c>
-      <c r="I34" s="4">
+      <c r="J34" s="4">
         <v>0.1156935280136379</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1982</v>
       </c>
@@ -29987,777 +30092,853 @@
         <v>239.70833333333334</v>
       </c>
       <c r="C35" s="4">
+        <v>7746.166666666667</v>
+      </c>
+      <c r="D35" s="4">
         <v>27.591666666666669</v>
       </c>
-      <c r="D35" s="4">
+      <c r="E35" s="4">
         <v>-0.87500000000000011</v>
       </c>
-      <c r="E35" s="4">
+      <c r="F35" s="4">
         <v>-0.22341666666666668</v>
       </c>
-      <c r="F35" s="4">
+      <c r="G35" s="4">
         <v>75.451820368826716</v>
       </c>
-      <c r="G35" s="4">
+      <c r="H35" s="4">
         <v>0.68018491246977453</v>
       </c>
-      <c r="H35" s="4">
+      <c r="I35" s="4">
         <v>1.2181394158156269</v>
       </c>
-      <c r="I35" s="4">
+      <c r="J35" s="4">
         <v>0.12162270895409842</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1981</v>
       </c>
       <c r="B36" s="4">
         <v>256.24583333333334</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="4">
+        <v>9255.3333333333339</v>
+      </c>
+      <c r="D36" s="9">
         <v>27.858333333333334</v>
       </c>
-      <c r="D36" s="4">
+      <c r="E36" s="4">
         <v>0.24166666666666659</v>
       </c>
-      <c r="E36" s="4">
+      <c r="F36" s="4">
         <v>-8.7249999999999994E-2</v>
       </c>
-      <c r="F36" s="4">
+      <c r="G36" s="4">
         <v>109.00659466775664</v>
       </c>
-      <c r="G36" s="4">
+      <c r="H36" s="4">
         <v>0.39418116124288299</v>
       </c>
-      <c r="H36" s="4">
+      <c r="I36" s="4">
         <v>0.67076392451013833</v>
       </c>
-      <c r="I36" s="4">
+      <c r="J36" s="4">
         <v>6.5570399363792775E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1980</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4">
+        <v>6208.416666666667</v>
+      </c>
+      <c r="D37" s="4">
         <v>28.108333333333334</v>
       </c>
-      <c r="D37" s="4">
+      <c r="E37" s="4">
         <v>-6.6666666666666666E-2</v>
       </c>
-      <c r="E37" s="4">
+      <c r="F37" s="4">
         <v>-2.9499999999999998E-2</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4">
+      <c r="G37" s="4"/>
+      <c r="H37" s="4">
         <v>0.48139632761626289</v>
       </c>
-      <c r="H37" s="4">
+      <c r="I37" s="4">
         <v>0.33393884397468881</v>
       </c>
-      <c r="I37" s="4">
+      <c r="J37" s="4">
         <v>0.11535439464379482</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1979</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4">
+        <v>7326.75</v>
+      </c>
+      <c r="D38" s="4">
         <v>28.099999999999998</v>
       </c>
-      <c r="D38" s="4">
+      <c r="E38" s="4">
         <v>0.14166666666666669</v>
       </c>
-      <c r="E38" s="4">
+      <c r="F38" s="4">
         <v>-0.12133333333333333</v>
       </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4">
+      <c r="G38" s="4"/>
+      <c r="H38" s="4">
         <v>0.46122366887148453</v>
       </c>
-      <c r="H38" s="4">
+      <c r="I38" s="4">
         <v>0.59917873086012607</v>
       </c>
-      <c r="I38" s="4">
+      <c r="J38" s="4">
         <v>6.3221592015463318E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1978</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4">
+        <v>6900.75</v>
+      </c>
+      <c r="D39" s="4">
         <v>28.133333333333336</v>
       </c>
-      <c r="D39" s="4">
+      <c r="E39" s="4">
         <v>-6.6666666666666707E-2</v>
       </c>
-      <c r="E39" s="4">
+      <c r="F39" s="4">
         <v>-0.19074999999999998</v>
       </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4">
+      <c r="G39" s="4"/>
+      <c r="H39" s="4">
         <v>0.43134743080329802</v>
       </c>
-      <c r="H39" s="4">
+      <c r="I39" s="4">
         <v>0.98195846360343797</v>
       </c>
-      <c r="I39" s="4">
+      <c r="J39" s="4">
         <v>6.3410817832463218E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1977</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
+        <v>5718</v>
+      </c>
+      <c r="D40" s="4">
         <v>27.691666666666666</v>
       </c>
-      <c r="D40" s="4">
+      <c r="E40" s="4">
         <v>-0.63333333333333341</v>
       </c>
-      <c r="E40" s="4">
+      <c r="F40" s="4">
         <v>-0.20025000000000004</v>
       </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4">
+      <c r="G40" s="4"/>
+      <c r="H40" s="4">
         <v>0.7488880646220315</v>
       </c>
-      <c r="H40" s="4">
+      <c r="I40" s="4">
         <v>0.64994172232919656</v>
       </c>
-      <c r="I40" s="4">
+      <c r="J40" s="4">
         <v>8.546676653423925E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1976</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
+        <v>7073.833333333333</v>
+      </c>
+      <c r="D41" s="4">
         <v>27.225000000000005</v>
       </c>
-      <c r="D41" s="9">
+      <c r="E41" s="9">
         <v>0.31666666666666671</v>
       </c>
-      <c r="E41" s="9">
+      <c r="F41" s="9">
         <v>-0.37458333333333343</v>
       </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4">
+      <c r="G41" s="4"/>
+      <c r="H41" s="4">
         <v>0.89759780424297908</v>
       </c>
-      <c r="H41" s="4">
+      <c r="I41" s="4">
         <v>0.96656216781044357</v>
       </c>
-      <c r="I41" s="4">
+      <c r="J41" s="4">
         <v>0.10912833007172038</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1975</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
+        <v>8841</v>
+      </c>
+      <c r="D42" s="4">
         <v>27.058333333333334</v>
       </c>
-      <c r="D42" s="4">
+      <c r="E42" s="4">
         <v>1.3333333333333333</v>
       </c>
-      <c r="E42" s="4">
+      <c r="F42" s="4">
         <v>-0.30933333333333335</v>
       </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4">
+      <c r="G42" s="4"/>
+      <c r="H42" s="4">
         <v>0.46992907266238948</v>
       </c>
-      <c r="H42" s="4">
+      <c r="I42" s="4">
         <v>0.76078109781189962</v>
       </c>
-      <c r="I42" s="4">
+      <c r="J42" s="4">
         <v>5.2567417031212121E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1974</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
+        <v>8906.5833333333339</v>
+      </c>
+      <c r="D43" s="4">
         <v>27.783333333333331</v>
       </c>
-      <c r="D43" s="4">
+      <c r="E43" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E43" s="4">
+      <c r="F43" s="4">
         <v>-0.4308333333333334</v>
       </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4">
+      <c r="G43" s="4"/>
+      <c r="H43" s="4">
         <v>0.44687466889159205</v>
       </c>
-      <c r="H43" s="4">
+      <c r="I43" s="4">
         <v>0.81463879335344902</v>
       </c>
-      <c r="I43" s="4">
+      <c r="J43" s="4">
         <v>8.7854045628719971E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1973</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
+        <v>6785.416666666667</v>
+      </c>
+      <c r="D44" s="4">
         <v>27.933333333333334</v>
       </c>
-      <c r="D44" s="4">
+      <c r="E44" s="4">
         <v>0.74166666666666659</v>
       </c>
-      <c r="E44" s="4">
+      <c r="F44" s="4">
         <v>-0.22575000000000001</v>
       </c>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4">
+      <c r="G44" s="4"/>
+      <c r="H44" s="4">
         <v>0.40301891075263707</v>
       </c>
-      <c r="H44" s="4">
+      <c r="I44" s="4">
         <v>1.0202123961868597</v>
       </c>
-      <c r="I44" s="4">
+      <c r="J44" s="4">
         <v>9.7302830940784596E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1972</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
+        <v>7173.75</v>
+      </c>
+      <c r="D45" s="4">
         <v>28.416666666666661</v>
       </c>
-      <c r="D45" s="4">
+      <c r="E45" s="4">
         <v>-0.48333333333333339</v>
       </c>
-      <c r="E45" s="4">
+      <c r="F45" s="4">
         <v>-0.36308333333333337</v>
       </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4">
+      <c r="G45" s="4"/>
+      <c r="H45" s="4">
         <v>1.3940349110884325</v>
       </c>
-      <c r="H45" s="4">
+      <c r="I45" s="4">
         <v>0.88403345610624451</v>
       </c>
-      <c r="I45" s="4">
+      <c r="J45" s="4">
         <v>7.0042140994914612E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1971</v>
       </c>
       <c r="B46" s="4"/>
-      <c r="C46" s="9">
+      <c r="C46" s="4">
+        <v>10321.083333333334</v>
+      </c>
+      <c r="D46" s="9">
         <v>27.866666666666671</v>
       </c>
-      <c r="D46" s="9">
+      <c r="E46" s="9">
         <v>1.1083333333333336</v>
       </c>
-      <c r="E46" s="9">
+      <c r="F46" s="9">
         <v>-0.32100000000000001</v>
       </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4">
+      <c r="G46" s="4"/>
+      <c r="H46" s="4">
         <v>0.3284490643597392</v>
       </c>
-      <c r="H46" s="4">
+      <c r="I46" s="4">
         <v>0.74156877120348164</v>
       </c>
-      <c r="I46" s="4">
+      <c r="J46" s="4">
         <v>6.4845270381956713E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1970</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
+        <v>8388.8333333333339</v>
+      </c>
+      <c r="D47" s="4">
         <v>27.575000000000003</v>
       </c>
-      <c r="D47" s="4">
+      <c r="E47" s="4">
         <v>0.47499999999999992</v>
       </c>
-      <c r="E47" s="4">
+      <c r="F47" s="4">
         <v>-0.112</v>
       </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4">
+      <c r="G47" s="4"/>
+      <c r="H47" s="4">
         <v>0.55779598746886272</v>
       </c>
-      <c r="H47" s="4">
+      <c r="I47" s="4">
         <v>0.96117825420867509</v>
       </c>
-      <c r="I47" s="4">
+      <c r="J47" s="4">
         <v>9.5611904926302796E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1969</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
+        <v>7425.666666666667</v>
+      </c>
+      <c r="D48" s="4">
         <v>27.500000000000004</v>
       </c>
-      <c r="D48" s="4">
+      <c r="E48" s="4">
         <v>-0.35000000000000003</v>
       </c>
-      <c r="E48" s="4">
+      <c r="F48" s="4">
         <v>1.08333333333334E-3</v>
       </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4">
+      <c r="G48" s="4"/>
+      <c r="H48" s="4">
         <v>0.43484584520368719</v>
       </c>
-      <c r="H48" s="4">
+      <c r="I48" s="4">
         <v>0.57761264151363911</v>
       </c>
-      <c r="I48" s="4">
+      <c r="J48" s="4">
         <v>0.12123340248787823</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1968</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
+        <v>7191.583333333333</v>
+      </c>
+      <c r="D49" s="4">
         <v>27.258333333333336</v>
       </c>
-      <c r="D49" s="4">
+      <c r="E49" s="4">
         <v>0.39166666666666666</v>
       </c>
-      <c r="E49" s="4">
+      <c r="F49" s="4">
         <v>-0.17533333333333334</v>
       </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4">
+      <c r="G49" s="4"/>
+      <c r="H49" s="4">
         <v>0.64308677957224869</v>
       </c>
-      <c r="H49" s="4">
+      <c r="I49" s="4">
         <v>0.56962241614046139</v>
       </c>
-      <c r="I49" s="4">
+      <c r="J49" s="4">
         <v>5.4877273543017226E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1967</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
+        <v>7275.416666666667</v>
+      </c>
+      <c r="D50" s="4">
         <v>27.691666666666663</v>
       </c>
-      <c r="D50" s="4">
+      <c r="E50" s="4">
         <v>0.47500000000000003</v>
       </c>
-      <c r="E50" s="4">
+      <c r="F50" s="4">
         <v>-0.10599999999999998</v>
       </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4">
+      <c r="G50" s="4"/>
+      <c r="H50" s="4">
         <v>0.64871668186761899</v>
       </c>
-      <c r="H50" s="4">
+      <c r="I50" s="4">
         <v>0.74969690845397952</v>
       </c>
-      <c r="I50" s="4">
+      <c r="J50" s="4">
         <v>0.11846441736579884</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1966</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
+        <v>7130.166666666667</v>
+      </c>
+      <c r="D51" s="4">
         <v>27.474999999999998</v>
       </c>
-      <c r="D51" s="4">
+      <c r="E51" s="4">
         <v>-0.21666666666666667</v>
       </c>
-      <c r="E51" s="4">
+      <c r="F51" s="4">
         <v>-3.6666666666666657E-3</v>
       </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4">
+      <c r="G51" s="4"/>
+      <c r="H51" s="4">
         <v>0.71493801384201416</v>
       </c>
-      <c r="H51" s="4">
+      <c r="I51" s="4">
         <v>0.50241839379569142</v>
       </c>
-      <c r="I51" s="4">
+      <c r="J51" s="4">
         <v>4.3749978354972997E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1965</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
+        <v>5808.666666666667</v>
+      </c>
+      <c r="D52" s="4">
         <v>27.641666666666666</v>
       </c>
-      <c r="D52" s="4">
+      <c r="E52" s="4">
         <v>-0.5083333333333333</v>
       </c>
-      <c r="E52" s="4">
+      <c r="F52" s="4">
         <v>-0.16716666666666669</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4">
+      <c r="G52" s="4"/>
+      <c r="H52" s="4">
         <v>0.69210920490566452</v>
       </c>
-      <c r="H52" s="4">
+      <c r="I52" s="4">
         <v>0.79938423271612724</v>
       </c>
-      <c r="I52" s="4">
+      <c r="J52" s="4">
         <v>6.4566855180338265E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1964</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
+        <v>7291</v>
+      </c>
+      <c r="D53" s="4">
         <v>27.450000000000003</v>
       </c>
-      <c r="D53" s="4">
+      <c r="E53" s="4">
         <v>0.61666666666666659</v>
       </c>
-      <c r="E53" s="4">
+      <c r="F53" s="4">
         <v>-0.10299999999999999</v>
       </c>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4">
+      <c r="G53" s="4"/>
+      <c r="H53" s="4">
         <v>0.54522722535904877</v>
       </c>
-      <c r="H53" s="4">
+      <c r="I53" s="4">
         <v>0.66172410253729486</v>
       </c>
-      <c r="I53" s="4">
+      <c r="J53" s="4">
         <v>0.1109045453613971</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1963</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
+        <v>7493.166666666667</v>
+      </c>
+      <c r="D54" s="4">
         <v>27.841666666666669</v>
       </c>
-      <c r="D54" s="4">
+      <c r="E54" s="4">
         <v>-4.1666666666666664E-2</v>
       </c>
-      <c r="E54" s="4">
+      <c r="F54" s="4">
         <v>-2.8333333333333314E-3</v>
       </c>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4">
+      <c r="G54" s="4"/>
+      <c r="H54" s="4">
         <v>0.23915887961137822</v>
       </c>
-      <c r="H54" s="4">
+      <c r="I54" s="4">
         <v>0.82512625296577091</v>
       </c>
-      <c r="I54" s="4">
+      <c r="J54" s="4">
         <v>0.11651050154255183</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1962</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
+        <v>7847.75</v>
+      </c>
+      <c r="D55" s="4">
         <v>27.858333333333331</v>
       </c>
-      <c r="D55" s="4">
+      <c r="E55" s="4">
         <v>0.53333333333333333</v>
       </c>
-      <c r="E55" s="4">
+      <c r="F55" s="4">
         <v>6.483333333333334E-2</v>
       </c>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4">
+      <c r="G55" s="4"/>
+      <c r="H55" s="4">
         <v>0.71789887023088983</v>
       </c>
-      <c r="H55" s="4">
+      <c r="I55" s="4">
         <v>0.60952042747979451</v>
       </c>
-      <c r="I55" s="4">
+      <c r="J55" s="4">
         <v>8.888995580167787E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1961</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
+        <v>6466</v>
+      </c>
+      <c r="D56" s="4">
         <v>27.341666666666665</v>
       </c>
-      <c r="D56" s="4">
+      <c r="E56" s="4">
         <v>0.18333333333333338</v>
       </c>
-      <c r="E56" s="9">
+      <c r="F56" s="9">
         <v>9.2833333333333337E-2</v>
       </c>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4">
+      <c r="G56" s="4"/>
+      <c r="H56" s="4">
         <v>1.0202123961868599</v>
       </c>
-      <c r="H56" s="4">
+      <c r="I56" s="4">
         <v>0.80660155008905143</v>
       </c>
-      <c r="I56" s="4">
+      <c r="J56" s="4">
         <v>8.4718607308208405E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1960</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4">
+        <v>7080.833333333333</v>
+      </c>
+      <c r="D57" s="4">
         <v>27.900000000000006</v>
       </c>
-      <c r="D57" s="4">
+      <c r="E57" s="4">
         <v>0.49999999999999994</v>
       </c>
-      <c r="E57" s="4">
+      <c r="F57" s="4">
         <v>0.22850000000000004</v>
       </c>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4">
+      <c r="G57" s="4"/>
+      <c r="H57" s="4">
         <v>0.70839126322829615</v>
       </c>
-      <c r="H57" s="4">
+      <c r="I57" s="4">
         <v>0.33028912953790823</v>
       </c>
-      <c r="I57" s="4">
+      <c r="J57" s="4">
         <v>8.5401192242050228E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1959</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
+        <v>5683.416666666667</v>
+      </c>
+      <c r="D58" s="4">
         <v>27.474999999999994</v>
       </c>
-      <c r="D58" s="4">
+      <c r="E58" s="4">
         <v>0.14166666666666669</v>
       </c>
-      <c r="E58" s="4">
+      <c r="F58" s="4">
         <v>4.6166666666666668E-2</v>
       </c>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4">
+      <c r="G58" s="4"/>
+      <c r="H58" s="4">
         <v>0.89658442790605952</v>
       </c>
-      <c r="H58" s="4">
+      <c r="I58" s="4">
         <v>0.77513439694889907</v>
       </c>
-      <c r="I58" s="4">
+      <c r="J58" s="4">
         <v>6.7265867791153705E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1958</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
+        <v>4849.333333333333</v>
+      </c>
+      <c r="D59" s="4">
         <v>28.333333333333329</v>
       </c>
-      <c r="D59" s="4">
+      <c r="E59" s="4">
         <v>-0.15</v>
       </c>
-      <c r="E59" s="4">
+      <c r="F59" s="4">
         <v>0.20758333333333334</v>
       </c>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4">
+      <c r="G59" s="4"/>
+      <c r="H59" s="4">
         <v>0.71647284200682282</v>
       </c>
-      <c r="H59" s="4">
+      <c r="I59" s="4">
         <v>0.72425510322361863</v>
       </c>
-      <c r="I59" s="4">
+      <c r="J59" s="4">
         <v>8.0404045955788719E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1957</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
+        <v>5915.166666666667</v>
+      </c>
+      <c r="D60" s="4">
         <v>28.108333333333334</v>
       </c>
-      <c r="D60" s="4">
+      <c r="E60" s="4">
         <v>-0.17499999999999996</v>
       </c>
-      <c r="E60" s="4">
+      <c r="F60" s="4">
         <v>3.4166666666666658E-2</v>
       </c>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4">
+      <c r="G60" s="4"/>
+      <c r="H60" s="4">
         <v>0.92092674008634356</v>
       </c>
-      <c r="H60" s="4">
+      <c r="I60" s="4">
         <v>0.50475016322209076</v>
       </c>
-      <c r="I60" s="4">
+      <c r="J60" s="4">
         <v>0.11841439818269439</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1956</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
+        <v>8566.4</v>
+      </c>
+      <c r="D61" s="4">
         <v>27.299999999999997</v>
       </c>
-      <c r="D61" s="4">
+      <c r="E61" s="4">
         <v>1.0916666666666668</v>
       </c>
-      <c r="E61" s="4">
+      <c r="F61" s="4">
         <v>-2.5416666666666667E-2</v>
       </c>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4">
+      <c r="G61" s="4"/>
+      <c r="H61" s="4">
         <v>0.57682516651692073</v>
       </c>
-      <c r="H61" s="4">
+      <c r="I61" s="4">
         <v>0.50173939873446649</v>
       </c>
-      <c r="I61" s="4">
+      <c r="J61" s="4">
         <v>0.11507978128501141</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1955</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
+        <v>8441.6</v>
+      </c>
+      <c r="D62" s="4">
         <v>27.641666666666666</v>
       </c>
-      <c r="D62" s="4">
+      <c r="E62" s="4">
         <v>1.0250000000000001</v>
       </c>
-      <c r="E62" s="4">
+      <c r="F62" s="4">
         <v>0.18641666666666667</v>
       </c>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4">
+      <c r="G62" s="4"/>
+      <c r="H62" s="4">
         <v>0.66940724570776866</v>
       </c>
-      <c r="H62" s="4">
+      <c r="I62" s="4">
         <v>0.70726746901527471</v>
       </c>
-      <c r="I62" s="4">
+      <c r="J62" s="4">
         <v>0.1059223200217399</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1954</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
+        <v>7888.25</v>
+      </c>
+      <c r="D63" s="4">
         <v>27.833333333333339</v>
       </c>
-      <c r="D63" s="4">
+      <c r="E63" s="4">
         <v>0.44999999999999996</v>
       </c>
-      <c r="E63" s="4">
+      <c r="F63" s="4">
         <v>3.7249999999999998E-2</v>
       </c>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4">
+      <c r="G63" s="4"/>
+      <c r="H63" s="4">
         <v>0.82278168244662353</v>
       </c>
-      <c r="H63" s="4">
+      <c r="I63" s="4">
         <v>0.46023709304898697</v>
       </c>
-      <c r="I63" s="4">
+      <c r="J63" s="4">
         <v>8.4774701414985831E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>1953</v>
-      </c>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
-      <c r="G64" s="4">
-        <v>9.5742710775633316E-2</v>
-      </c>
-      <c r="H64" s="4">
-        <v>0.64308677957224869</v>
-      </c>
-      <c r="I64" s="4">
-        <v>6.6929349905612209E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>1952</v>
-      </c>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>1951</v>
-      </c>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{E5663368-DD9B-49CC-86B8-C45DECA5C9AE}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I67">
+  <autoFilter ref="A1:J1" xr:uid="{E5663368-DD9B-49CC-86B8-C45DECA5C9AE}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J67">
       <sortCondition descending="1" ref="A1"/>
     </sortState>
   </autoFilter>
@@ -30773,7 +30954,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -32022,17 +32203,17 @@
         <v>0</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
       <c r="E1" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F1" s="19"/>
       <c r="G1" s="19"/>
       <c r="H1" s="19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I1" s="19"/>
       <c r="J1" s="19"/>
@@ -32040,31 +32221,31 @@
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="20"/>
       <c r="B2" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -32197,7 +32378,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="16">
@@ -32229,52 +32410,52 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="18"/>
       <c r="B15" s="18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I15" s="18"/>
       <c r="J15" s="18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M15" s="18"/>
       <c r="N15" s="18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>0.69398659982087496</v>
@@ -32283,7 +32464,7 @@
         <v>0.76999541251457271</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F16">
         <v>1.0569666904762018</v>
@@ -32292,7 +32473,7 @@
         <v>0.99357220430108217</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J16">
         <v>0.72722999409079758</v>
@@ -32301,7 +32482,7 @@
         <v>0.76586545174882625</v>
       </c>
       <c r="M16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N16">
         <v>1.0105710444247793</v>
@@ -32312,7 +32493,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>2.5561939641074727E-3</v>
@@ -32321,7 +32502,7 @@
         <v>4.7306255559927124E-3</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F17">
         <v>1.8318792757706898E-2</v>
@@ -32330,7 +32511,7 @@
         <v>1.4810465728220498E-2</v>
       </c>
       <c r="I17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J17">
         <v>1.0465107062389227E-2</v>
@@ -32339,7 +32520,7 @@
         <v>1.0497642107921716E-2</v>
       </c>
       <c r="M17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N17">
         <v>3.1388125505090651E-4</v>
@@ -32350,7 +32531,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B18">
         <v>35</v>
@@ -32359,7 +32540,7 @@
         <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F18">
         <v>35</v>
@@ -32368,7 +32549,7 @@
         <v>31</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J18">
         <v>35</v>
@@ -32377,7 +32558,7 @@
         <v>31</v>
       </c>
       <c r="M18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N18">
         <v>35</v>
@@ -32388,25 +32569,25 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -32414,25 +32595,25 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F20">
         <v>64</v>
       </c>
       <c r="I20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J20">
         <v>63</v>
       </c>
       <c r="M20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N20">
         <v>59</v>
@@ -32440,25 +32621,25 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B21">
         <v>-5.0601195197012308</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F21">
         <v>2.0035569208729558</v>
       </c>
       <c r="I21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J21">
         <v>-1.5300281342770661</v>
       </c>
       <c r="M21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N21">
         <v>-4.4147236168248876</v>
@@ -32466,25 +32647,25 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B22">
         <v>2.4987787362421829E-6</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F22">
         <v>2.4677555035338326E-2</v>
       </c>
       <c r="I22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J22">
         <v>6.5507915110529225E-2</v>
       </c>
       <c r="M22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N22">
         <v>2.1870701059378568E-5</v>
@@ -32492,25 +32673,25 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B23">
         <v>1.673033965289912</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F23">
         <v>1.6690130250240895</v>
       </c>
       <c r="I23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J23">
         <v>1.6694022217068125</v>
       </c>
       <c r="M23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N23">
         <v>1.6710930321038957</v>
@@ -32518,25 +32699,25 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B24">
         <v>4.9975574724843657E-6</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F24">
         <v>4.9355110070676653E-2</v>
       </c>
       <c r="I24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J24">
         <v>0.13101583022105845</v>
       </c>
       <c r="M24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N24">
         <v>4.3741402118757136E-5</v>
@@ -32544,28 +32725,28 @@
     </row>
     <row r="25" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" s="17">
         <v>2.0040447832891455</v>
       </c>
       <c r="C25" s="17"/>
       <c r="E25" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F25" s="17">
         <v>1.9977296543176954</v>
       </c>
       <c r="G25" s="17"/>
       <c r="I25" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J25" s="17">
         <v>1.9983405425207412</v>
       </c>
       <c r="K25" s="17"/>
       <c r="M25" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N25" s="17">
         <v>2.0009953780882688</v>
@@ -32593,10 +32774,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
